--- a/sources/lee_step8.xlsx
+++ b/sources/lee_step8.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB128"/>
+  <dimension ref="A1:AB129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col hidden="1" min="1" max="1"/>
@@ -5747,77 +5747,77 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>b+3~3 [~4]</t>
+          <t>b+3~3</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>b+3~3 [~4]</t>
+          <t>b+3~3</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Feint Mist Wolf [Mist Trap]</t>
+          <t>Feint Mist Wolf</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Feint Mist Wolf [Mist Trap]</t>
+          <t>Feint Mist Wolf</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>14 x</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>14 x</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>-8 x</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>-8 x</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>+3 x</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>+3 x</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>+3 x</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>+3 x</t>
+          <t>+3</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>18 [33]</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>18 [33]</t>
+          <t>18</t>
         </is>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>18 [33]</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -5828,11 +5828,6 @@
       <c r="S64" t="inlineStr">
         <is>
           <t>h</t>
-        </is>
-      </c>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>If the High Kick is blocked, tapping 4 at the exact frame will cause the opponent to grab Lee's foot. Lee will auto reverse.</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
@@ -5849,216 +5844,181 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>b+3&lt;3</t>
+          <t>b+3~3:4</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>b+3&lt;3</t>
+          <t>b+3~3:4</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Mist Wolf Combo</t>
+          <t>Mist Trap</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Mist Wolf Combo</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>-8 -10</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>-8 -10</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>+3 +1</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>+3 +1</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>+3 +1</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>+3 +1</t>
+          <t>Mist Trap</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>18,18</t>
+          <t>33</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>33</t>
         </is>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>18,18</t>
-        </is>
-      </c>
-      <c r="R65" t="inlineStr">
-        <is>
-          <t>mh</t>
-        </is>
-      </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>mh</t>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>If the High Kick is blocked, tapping 4 at the exact frame will cause the opponent to grab Lee's foot. Lee will auto reverse.</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>f4cc96ee-83f7-47a9-b87e-93696b5170ad</t>
+          <t>6d339f6a-39b1-4eb1-bcd3-ded0f8935a0c</t>
         </is>
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>76208997-8a95-4c34-b583-1d57608fb563</t>
+          <t>c92e1826-7388-447a-858b-7a3d0c9ce2f3</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>a1226d52-19ca-4e28-a360-74af905c7295</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>d+3,3</t>
+          <t>b+3&lt;3</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>d+3,3</t>
+          <t>b+3&lt;3</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Silver Low - Head Kick</t>
+          <t>Mist Wolf Combo</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Silver Low - Head Kick</t>
+          <t>Mist Wolf Combo</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>-14 -14</t>
+          <t>-8 -10</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>-14 -14</t>
+          <t>-8 -10</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>-3 -3</t>
+          <t>+3 +1</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>-3 -3</t>
+          <t>+3 +1</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>-3 -3</t>
+          <t>+3 +1</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>-3 -3</t>
+          <t>+3 +1</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>8,18</t>
+          <t>18,18</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>36</t>
         </is>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>8,18</t>
+          <t>18,18</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
         <is>
-          <t>lh</t>
+          <t>mh</t>
         </is>
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>lh</t>
+          <t>mh</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>4f347fe7-94ca-4393-9f81-36a0fc28c63e</t>
+          <t>f4cc96ee-83f7-47a9-b87e-93696b5170ad</t>
         </is>
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>48a0bff1-515e-4838-b9d8-47112a7d184b</t>
+          <t>76208997-8a95-4c34-b583-1d57608fb563</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>– f+3</t>
+          <t>d+3,3</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>d+3,3,f+3</t>
+          <t>d+3,3</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>– Step In Kick</t>
+          <t>Silver Low - Head Kick</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Silver Low - Head Kick – Step In Kick</t>
+          <t>Silver Low - Head Kick</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>16</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -6068,94 +6028,89 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-14 -14</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>-14 -14 -13</t>
+          <t>-14 -14</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-3 -3</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>-3 -3 -8</t>
+          <t>-3 -3</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-3 -3</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>-3 -3 -8</t>
+          <t>-3 -3</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8,18</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>26</t>
         </is>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>8,18,15</t>
+          <t>8,18</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>lh</t>
         </is>
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>lhm</t>
+          <t>lh</t>
         </is>
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>802161b3-03e3-4cc2-937c-49282739b656</t>
+          <t>4f347fe7-94ca-4393-9f81-36a0fc28c63e</t>
         </is>
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>739dc695-990a-48f5-bc77-a80b9d90e70e</t>
-        </is>
-      </c>
-      <c r="AA67" t="inlineStr">
-        <is>
-          <t>4f347fe7-94ca-4393-9f81-36a0fc28c63e</t>
+          <t>48a0bff1-515e-4838-b9d8-47112a7d184b</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>– b+3</t>
+          <t>– f+3</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>d+3,3,b+3</t>
+          <t>d+3,3,f+3</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>– Feint Hammer</t>
+          <t>– Step In Kick</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Silver Low - Head Kick – Feint Hammer</t>
+          <t>Silver Low - Head Kick – Step In Kick</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -6165,47 +6120,47 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>-14 -14 -14</t>
+          <t>-14 -14 -13</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>-3 -3 -9</t>
+          <t>-3 -3 -8</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>-3 -3 KD</t>
+          <t>-3 -3 -8</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>15</t>
         </is>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>8,18,19</t>
+          <t>8,18,15</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
@@ -6218,19 +6173,14 @@
           <t>lhm</t>
         </is>
       </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>KSco GB</t>
-        </is>
-      </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>d7eadaff-38fb-4d5e-bce7-d9b8d1f518fa</t>
+          <t>802161b3-03e3-4cc2-937c-49282739b656</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>271d0c73-2e1c-43a9-a7e9-b3190c487b2f</t>
+          <t>739dc695-990a-48f5-bc77-a80b9d90e70e</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -6242,22 +6192,22 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>– 3,f+3</t>
+          <t>– b+3</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>d+3,3,3,f+3</t>
+          <t>d+3,3,b+3</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>– Double Head Kick - Step In Kick</t>
+          <t>– Feint Hammer</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Silver Low - Head Kick – Double Head Kick - Step In Kick</t>
+          <t>Silver Low - Head Kick – Feint Hammer</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -6267,67 +6217,72 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>-14 -13</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>-14 -14 -14 -13</t>
+          <t>-14 -14 -14</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>-3 -8</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>-3 -3 -3 -8</t>
+          <t>-3 -3 -9</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>-3 -8</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>-3 -3 -3 -8</t>
+          <t>-3 -3 KD</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>10,15</t>
+          <t>19</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>19</t>
         </is>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>8,18,10,15</t>
+          <t>8,18,19</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>hm</t>
+          <t>m</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>lhhm</t>
+          <t>lhm</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>KSco GB</t>
         </is>
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>3477651c-4aee-4866-9e47-d439d82480cd</t>
+          <t>d7eadaff-38fb-4d5e-bce7-d9b8d1f518fa</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>47d4e33f-25c7-4c10-92e8-1ef76c9a3794</t>
+          <t>271d0c73-2e1c-43a9-a7e9-b3190c487b2f</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -6339,22 +6294,22 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>– 3,b+3</t>
+          <t>– 3,f+3</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>d+3,3,3,b+3</t>
+          <t>d+3,3,3,f+3</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>– Double Head Kick - Feint Hammer</t>
+          <t>– Double Head Kick - Step In Kick</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Silver Low - Head Kick – Double Head Kick - Feint Hammer</t>
+          <t>Silver Low - Head Kick – Double Head Kick - Step In Kick</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -6364,47 +6319,47 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>-14 -14</t>
+          <t>-14 -13</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>-14 -14 -14 -14</t>
+          <t>-14 -14 -14 -13</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>-3 -9</t>
+          <t>-3 -8</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>-3 -3 -3 -9</t>
+          <t>-3 -3 -3 -8</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>-3 KD</t>
+          <t>-3 -8</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>-3 -3 -3 KD</t>
+          <t>-3 -3 -3 -8</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>10,19</t>
+          <t>10,15</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>8,18,10,19</t>
+          <t>8,18,10,15</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
@@ -6417,19 +6372,14 @@
           <t>lhhm</t>
         </is>
       </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>KSco GB</t>
-        </is>
-      </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>a6e50724-490e-41e8-a483-9fed08c530ec</t>
+          <t>3477651c-4aee-4866-9e47-d439d82480cd</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>b56b8e86-6d36-4cc7-8234-cdb5c27c53ef</t>
+          <t>47d4e33f-25c7-4c10-92e8-1ef76c9a3794</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -6441,22 +6391,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>– 3,3,b+3</t>
+          <t>– 3,b+3</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>d+3,3,3,3,b+3</t>
+          <t>d+3,3,3,b+3</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>– Triple Head Kick - Feint Hammer</t>
+          <t>– Double Head Kick - Feint Hammer</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Silver Low - Head Kick – Triple Head Kick - Feint Hammer</t>
+          <t>Silver Low - Head Kick – Double Head Kick - Feint Hammer</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -6466,57 +6416,57 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>-14 -14 -14</t>
+          <t>-14 -14</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>-14 -14 -14 -14 -14</t>
+          <t>-14 -14 -14 -14</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>-3 KD -9</t>
+          <t>-3 -9</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>-3 -3 -3 KD -9</t>
+          <t>-3 -3 -3 -9</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>-3 KD -9</t>
+          <t>-3 KD</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>-3 -3 -3 KD -9</t>
+          <t>-3 -3 -3 KD</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>10,10,19</t>
+          <t>10,19</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>29</t>
         </is>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>8,18,10,10,19</t>
+          <t>8,18,10,19</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
         <is>
-          <t>hhm</t>
+          <t>hm</t>
         </is>
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>lhhhm</t>
+          <t>lhhm</t>
         </is>
       </c>
       <c r="V71" t="inlineStr">
@@ -6526,12 +6476,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>05bfab7f-eb6e-4e32-b78c-8aab9723675a</t>
+          <t>a6e50724-490e-41e8-a483-9fed08c530ec</t>
         </is>
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>4586d518-d522-436b-a50a-dd82057c0eb5</t>
+          <t>b56b8e86-6d36-4cc7-8234-cdb5c27c53ef</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -6543,119 +6493,129 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>WS+3,3</t>
+          <t>– 3,3,b+3</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>WS+3,3</t>
+          <t>d+3,3,3,3,b+3</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Tsunami Kick</t>
+          <t>– Triple Head Kick - Feint Hammer</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Tsunami Kick</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>Silver Low - Head Kick – Triple Head Kick - Feint Hammer</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>-21 -19</t>
+          <t>-14 -14 -14</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>-21 -19</t>
+          <t>-14 -14 -14 -14 -14</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>-10 -8</t>
+          <t>-3 KD -9</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>-10 -8</t>
+          <t>-3 -3 -3 KD -9</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>-10 -8</t>
+          <t>-3 KD -9</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>-10 -8</t>
+          <t>-3 -3 -3 KD -9</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>10,17</t>
+          <t>10,10,19</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>39</t>
         </is>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>10,17</t>
+          <t>8,18,10,10,19</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>hhm</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>lhhhm</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>KSco GB</t>
         </is>
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>3b938f5e-1c44-4a9c-94f0-afd9e8ec920d</t>
+          <t>05bfab7f-eb6e-4e32-b78c-8aab9723675a</t>
         </is>
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>bb9b4bdf-a50c-428b-a4a6-ed06b8be1515</t>
+          <t>4586d518-d522-436b-a50a-dd82057c0eb5</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>4f347fe7-94ca-4393-9f81-36a0fc28c63e</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>– df+3</t>
+          <t>WS+3,3</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>WS+3,3,df+3</t>
+          <t>WS+3,3</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>– Step In Kick Infinite Starter</t>
+          <t>Tsunami Kick</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Tsunami Kick – Step In Kick Infinite Starter</t>
+          <t>Tsunami Kick</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -6665,99 +6625,89 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-21 -19</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>-21 -19 -14</t>
+          <t>-21 -19</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-10 -8</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>-10 -8 -3</t>
+          <t>-10 -8</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-10 -8</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>-10 -8 -3</t>
+          <t>-10 -8</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10,17</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>10,17,15</t>
+          <t>10,17</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>mmm</t>
-        </is>
-      </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>The Infinite Kicks have to be started with 1 Silver Low or 1 Step In Kick after the WS+3,3.</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>0837029d-5cb6-40fc-a4af-20a4bfe29a3d</t>
+          <t>3b938f5e-1c44-4a9c-94f0-afd9e8ec920d</t>
         </is>
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>84540a36-e5cc-42ef-863f-4c7948ecf4b5</t>
-        </is>
-      </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>3b938f5e-1c44-4a9c-94f0-afd9e8ec920d</t>
+          <t>bb9b4bdf-a50c-428b-a4a6-ed06b8be1515</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>– D+3</t>
+          <t>– df+3</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>WS+3,3,D+3</t>
+          <t>WS+3,3,df+3</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>– Silver Low Infinite Starter</t>
+          <t>– Step In Kick Infinite Starter</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Tsunami Kick – Silver Low Infinite Starter</t>
+          <t>Tsunami Kick – Step In Kick Infinite Starter</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -6767,32 +6717,32 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>-21 -19 -19</t>
+          <t>-21 -19 -14</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>-10 -8 -8</t>
+          <t>-10 -8 -3</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>-8</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>-10 -8 -8</t>
+          <t>-10 -8 -3</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -6812,12 +6762,12 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>m</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>mml</t>
+          <t>mmm</t>
         </is>
       </c>
       <c r="W74" t="inlineStr">
@@ -6827,12 +6777,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>04b267ca-2bdf-4bf5-9a19-f3577401ddb8</t>
+          <t>0837029d-5cb6-40fc-a4af-20a4bfe29a3d</t>
         </is>
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>e0005f9f-f48b-428a-a294-6bd7747daaaf</t>
+          <t>84540a36-e5cc-42ef-863f-4c7948ecf4b5</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -6844,22 +6794,22 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>–– 3,3,3,3...</t>
+          <t>– D+3</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>WS+3,3,D+3,3,3,3,3...</t>
+          <t>WS+3,3,D+3</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>–– Rave Kicks</t>
+          <t>– Silver Low Infinite Starter</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Tsunami Kick – Silver Low Infinite Starter – Rave Kicks</t>
+          <t>Tsunami Kick – Silver Low Infinite Starter</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -6869,99 +6819,99 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>-19 -16 -19 -16...</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>-21 -19 -19 -19 -16 -19 -16...</t>
+          <t>-21 -19 -19</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>-8 -5 -8 -5...</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>-10 -8 -8 -8 -5 -8 -5...</t>
+          <t>-10 -8 -8</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>-8 -5 -8 -5...</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>-10 -8 -8 -8 -5 -8 -5...</t>
+          <t>-10 -8 -8</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>10,15,10,15...</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>10,15,10,15...</t>
+          <t>15</t>
         </is>
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>10,17,15,10,15,10,15...</t>
+          <t>10,17,15</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>mhmh</t>
+          <t>l</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>mmlmhmh</t>
+          <t>mml</t>
         </is>
       </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>Sequence of the Infinite is 2 Rave Kicks, Feint Hammer or Low Silver, 2 Rave Kicks, Feint Hammer or Silver Low...</t>
+          <t>The Infinite Kicks have to be started with 1 Silver Low or 1 Step In Kick after the WS+3,3.</t>
         </is>
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>243a8a43-ac3f-44fb-8421-37c65ea165a4</t>
+          <t>04b267ca-2bdf-4bf5-9a19-f3577401ddb8</t>
         </is>
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>5a1eea22-ebde-4c24-9859-dea8bdcea0a7</t>
+          <t>e0005f9f-f48b-428a-a294-6bd7747daaaf</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>04b267ca-2bdf-4bf5-9a19-f3577401ddb8</t>
+          <t>3b938f5e-1c44-4a9c-94f0-afd9e8ec920d</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>––– u+3,3,3...</t>
+          <t>–– 3,3,3,3...</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>WS+3,3,D+3,3,3,3,3...,u+3,3,3...</t>
+          <t>WS+3,3,D+3,3,3,3,3...</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>––– Feint Hammer - Rave Kicks</t>
+          <t>–– Rave Kicks</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Tsunami Kick – Silver Low Infinite Starter – Rave Kicks – Feint Hammer - Rave Kicks</t>
+          <t>Tsunami Kick – Silver Low Infinite Starter – Rave Kicks</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -6971,57 +6921,57 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>-19 -16 -19...</t>
+          <t>-19 -16 -19 -16...</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>-21 -19 -19 -19 -16 -19 -16... -19 -16 -19...</t>
+          <t>-21 -19 -19 -19 -16 -19 -16...</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>-8 -5 -8...</t>
+          <t>-8 -5 -8 -5...</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>-10 -8 -8 -8 -5 -8 -5... -8 -5 -8...</t>
+          <t>-10 -8 -8 -8 -5 -8 -5...</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>-8 -5 -8...</t>
+          <t>-8 -5 -8 -5...</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>-10 -8 -8 -8 -5 -8 -5... -8 -5 -8...</t>
+          <t>-10 -8 -8 -8 -5 -8 -5...</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>15,10,15...</t>
+          <t>10,15,10,15...</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>15,10,15...</t>
+          <t>10,15,10,15...</t>
         </is>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
-          <t>10,17,15,10,15,10,15...,15,10,15...</t>
+          <t>10,17,15,10,15,10,15...</t>
         </is>
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>mmh</t>
+          <t>mhmh</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>mmlmhmhmmh</t>
+          <t>mmlmhmh</t>
         </is>
       </c>
       <c r="W76" t="inlineStr">
@@ -7031,39 +6981,39 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>39fb6bb0-f725-4b5e-a7d2-5bfc7232d54f</t>
+          <t>243a8a43-ac3f-44fb-8421-37c65ea165a4</t>
         </is>
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>1ba56d81-9cf5-46be-896c-599b81b9877c</t>
+          <t>5a1eea22-ebde-4c24-9859-dea8bdcea0a7</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>243a8a43-ac3f-44fb-8421-37c65ea165a4</t>
+          <t>04b267ca-2bdf-4bf5-9a19-f3577401ddb8</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>––– d+3,3,3...</t>
+          <t>––– u+3,3,3...</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>WS+3,3,D+3,3,3,3,3...,d+3,3,3...</t>
+          <t>WS+3,3,D+3,3,3,3,3...,u+3,3,3...</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>––– Silver Low - Rave Kicks</t>
+          <t>––– Feint Hammer - Rave Kicks</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Tsunami Kick – Silver Low Infinite Starter – Rave Kicks – Silver Low - Rave Kicks</t>
+          <t>Tsunami Kick – Silver Low Infinite Starter – Rave Kicks – Feint Hammer - Rave Kicks</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -7118,12 +7068,12 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>lmh</t>
+          <t>mmh</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>mmlmhmhlmh</t>
+          <t>mmlmhmhmmh</t>
         </is>
       </c>
       <c r="W77" t="inlineStr">
@@ -7133,12 +7083,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>56cfa154-73bf-4cd4-b189-a9aadc2a8a62</t>
+          <t>39fb6bb0-f725-4b5e-a7d2-5bfc7232d54f</t>
         </is>
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>24c19ca0-22b4-469a-adef-ea81183b31ee</t>
+          <t>1ba56d81-9cf5-46be-896c-599b81b9877c</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -7150,124 +7100,134 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>f,f,N+3,4</t>
+          <t>––– d+3,3,3...</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>f,f,N+3,4</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>WR+3+4,4</t>
+          <t>WS+3,3,D+3,3,3,3,3...,d+3,3,3...</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Shredder</t>
+          <t>––– Silver Low - Rave Kicks</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Shredder</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>15</t>
+          <t>Tsunami Kick – Silver Low Infinite Starter – Rave Kicks – Silver Low - Rave Kicks</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>-17 -13</t>
+          <t>-19 -16 -19...</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>-17 -13</t>
+          <t>-21 -19 -19 -19 -16 -19 -16... -19 -16 -19...</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>-8 -5 -8...</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>-10 -8 -8 -8 -5 -8 -5... -8 -5 -8...</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>-8 -5 -8...</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>-10 -8 -8 -8 -5 -8 -5... -8 -5 -8...</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>20,15</t>
+          <t>15,10,15...</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>15,10,15...</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
         <is>
-          <t>20,15</t>
+          <t>10,17,15,10,15,10,15...,15,10,15...</t>
         </is>
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>lmh</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>mmlmhmhlmh</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Sequence of the Infinite is 2 Rave Kicks, Feint Hammer or Low Silver, 2 Rave Kicks, Feint Hammer or Silver Low...</t>
         </is>
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>65795a59-7c46-4715-bf24-aad915b6200c</t>
+          <t>56cfa154-73bf-4cd4-b189-a9aadc2a8a62</t>
         </is>
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>a7b92542-db99-45c4-9125-865afbd422b8</t>
+          <t>24c19ca0-22b4-469a-adef-ea81183b31ee</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>243a8a43-ac3f-44fb-8421-37c65ea165a4</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>– 4</t>
+          <t>f,f,N+3,4</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>f,f,N+3,4,4</t>
+          <t>f,f,N+3,4</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>WR+3+4,4</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>– Shredder Combo</t>
+          <t>Shredder</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Shredder – Shredder Combo</t>
+          <t>Shredder</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>15</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -7277,99 +7237,89 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-17 -13</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>-17 -13 -5</t>
+          <t>-17 -13</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>KD KD KD</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>KD KD KD</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20,15</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>35</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
         <is>
-          <t>20,15,25</t>
+          <t>20,15</t>
         </is>
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>mmh</t>
-        </is>
-      </c>
-      <c r="V79" t="inlineStr">
-        <is>
-          <t>GB</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>3b7304e0-d493-4f22-a5c4-d2c24328c38d</t>
+          <t>65795a59-7c46-4715-bf24-aad915b6200c</t>
         </is>
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>c4d97fa1-ed12-485d-8f46-b3f9e474d9cc</t>
-        </is>
-      </c>
-      <c r="AA79" t="inlineStr">
-        <is>
-          <t>65795a59-7c46-4715-bf24-aad915b6200c</t>
+          <t>a7b92542-db99-45c4-9125-865afbd422b8</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>– f+4</t>
+          <t>– 4</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>f,f,N+3,4,f+4</t>
+          <t>f,f,N+3,4,4</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>– Mid Shredder</t>
+          <t>– Shredder Combo</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Shredder – Mid Shredder</t>
+          <t>Shredder – Shredder Combo</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -7379,67 +7329,72 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>-17 -13 -14</t>
+          <t>-17 -13 -5</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>KD KD -3</t>
+          <t>KD KD KD</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>KD KD -3</t>
+          <t>KD KD KD</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>25</t>
         </is>
       </c>
       <c r="Q80" t="inlineStr">
         <is>
-          <t>20,15,15</t>
+          <t>20,15,25</t>
         </is>
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>h</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>mmm</t>
+          <t>mmh</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>GB</t>
         </is>
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>15b61dee-5770-4b5c-b544-109035fab466</t>
+          <t>3b7304e0-d493-4f22-a5c4-d2c24328c38d</t>
         </is>
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>62a77dc3-7da7-4a5d-a728-cebeced81a2e</t>
+          <t>c4d97fa1-ed12-485d-8f46-b3f9e474d9cc</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -7451,22 +7406,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>– d+4</t>
+          <t>– f+4</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>f,f,N+3,4,d+4</t>
+          <t>f,f,N+3,4,f+4</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>– Low Shredder</t>
+          <t>– Mid Shredder</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Shredder – Low Shredder</t>
+          <t>Shredder – Mid Shredder</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -7476,32 +7431,32 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>-22</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>-17 -13 -22</t>
+          <t>-17 -13 -14</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>KD KD -11</t>
+          <t>KD KD -3</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>KD KD -11</t>
+          <t>KD KD -3</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -7521,27 +7476,22 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>m</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>mmL</t>
-        </is>
-      </c>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>mmm</t>
         </is>
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>553afa99-1650-4b63-a19c-56a5ba447eaf</t>
+          <t>15b61dee-5770-4b5c-b544-109035fab466</t>
         </is>
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>b22455d8-7db7-4275-8a05-063f61af709a</t>
+          <t>62a77dc3-7da7-4a5d-a728-cebeced81a2e</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -7553,129 +7503,144 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>f+3+4</t>
+          <t>– d+4</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>f+3+4</t>
+          <t>f,f,N+3,4,d+4</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Silver Sting</t>
+          <t>– Low Shredder</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Silver Sting</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>25</t>
+          <t>Shredder – Low Shredder</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-22</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-17 -13 -22</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD KD -11</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD KD -11</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20,15,15</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>L</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>mmL</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>RC</t>
         </is>
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>1fdbb5aa-6456-4a50-a267-904bdd459b36</t>
+          <t>553afa99-1650-4b63-a19c-56a5ba447eaf</t>
         </is>
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>8fb7d6f7-8255-4ad9-9d3b-d3d8287e08ba</t>
+          <t>b22455d8-7db7-4275-8a05-063f61af709a</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>65795a59-7c46-4715-bf24-aad915b6200c</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>f,f,N+3+4</t>
+          <t>f+3+4</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>f,f,N+3+4</t>
+          <t>f+3+4</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Delayed Dragon Slide</t>
+          <t>Silver Sting</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Delayed Dragon Slide</t>
+          <t>Silver Sting</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>-2</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -7700,350 +7665,325 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>h</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>h</t>
         </is>
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>30151879-4344-4d6d-a1d1-cb7fac8501a0</t>
+          <t>1fdbb5aa-6456-4a50-a267-904bdd459b36</t>
         </is>
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>211e8d71-a7cd-49e0-a02f-2210c6ccd7ce</t>
+          <t>8fb7d6f7-8255-4ad9-9d3b-d3d8287e08ba</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>b,b,N+3+4</t>
+          <t>f,f,N+3+4</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>b,b,N+3+4</t>
+          <t>f,f,N+3+4</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Handspring Backflip</t>
+          <t>Delayed Dragon Slide</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Handspring Backflip</t>
+          <t>Delayed Dragon Slide</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>KD</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>L</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>L</t>
         </is>
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>d5959211-c39c-4522-b054-841f0967c06a</t>
+          <t>30151879-4344-4d6d-a1d1-cb7fac8501a0</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>087b8a78-ef8d-4211-b8ab-ba1a8e674123</t>
+          <t>211e8d71-a7cd-49e0-a02f-2210c6ccd7ce</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>4,3,4</t>
+          <t>b,b,N+3+4</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>4,3,4</t>
+          <t>b,b,N+3+4</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Shoalin Spin Kicks</t>
+          <t>Handspring Backflip</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Shoalin Spin Kicks</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>-4 -14 -6</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>-4 -14 -6</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>+5 -17 -1</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>+5 -17 -1</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>KD -17 KD</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>KD -17 KD</t>
+          <t>Handspring Backflip</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>16,12,12</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>16,12,12</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>hhh</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>hhh</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>3f43c9d8-9e07-4905-9503-5995a117e3df</t>
+          <t>d5959211-c39c-4522-b054-841f0967c06a</t>
         </is>
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>9e1e5af0-f868-4ab4-894c-47db0287e4d2</t>
+          <t>087b8a78-ef8d-4211-b8ab-ba1a8e674123</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>FC+ub+4</t>
+          <t>4,3,4</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>FC+ub+4</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>FC+u+4; FC+uf+4</t>
+          <t>4,3,4</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Quick Catapult</t>
+          <t>Shoalin Spin Kicks</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Quick Catapult</t>
+          <t>Shoalin Spin Kicks</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>-4 -14 -6</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>-16</t>
+          <t>-4 -14 -6</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+5 -17 -1</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+5 -17 -1</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD -17 KD</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD -17 KD</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>15_22_25</t>
+          <t>16,12,12</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>152225</t>
+          <t>40</t>
         </is>
       </c>
       <c r="Q86" t="inlineStr">
         <is>
-          <t>15_22_25</t>
+          <t>16,12,12</t>
         </is>
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>hhh</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>JG</t>
-        </is>
-      </c>
-      <c r="X86" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+          <t>hhh</t>
         </is>
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>cf9868ca-2157-404c-9914-37107239cf74</t>
+          <t>3f43c9d8-9e07-4905-9503-5995a117e3df</t>
         </is>
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>7517007f-8b73-4cc8-90de-b7de554a4a56</t>
+          <t>9e1e5af0-f868-4ab4-894c-47db0287e4d2</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>FC+UB+4</t>
+          <t>FC+ub+4</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>FC+UB+4</t>
+          <t>FC+ub+4</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>FC+U+4; FC+UF+4</t>
+          <t>FC+u+4; FC+uf+4</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>High Catapult Kick</t>
+          <t>Quick Catapult</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>High Catapult Kick</t>
+          <t>Quick Catapult</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>-31</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>-31</t>
+          <t>-16</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -8068,17 +8008,17 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>25_28_30</t>
+          <t>15_22_25</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>252830</t>
+          <t>152225</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
         <is>
-          <t>25_28_30</t>
+          <t>15_22_25</t>
         </is>
       </c>
       <c r="R87" t="inlineStr">
@@ -8091,51 +8031,71 @@
           <t>m</t>
         </is>
       </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>8e5621a5-277d-4d92-91cc-605997169c4a</t>
+          <t>cf9868ca-2157-404c-9914-37107239cf74</t>
         </is>
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>d51c082a-af11-40a0-a5eb-cc54a6413356</t>
+          <t>7517007f-8b73-4cc8-90de-b7de554a4a56</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>FC+UB+3+4</t>
+          <t>FC+UB+4</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>FC+UB+3+4</t>
+          <t>FC+UB+4</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>FC+U+3+4; FC+UF+3+4</t>
+          <t>FC+U+4; FC+UF+4</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Rainbow Kick</t>
+          <t>High Catapult Kick</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Rainbow Kick</t>
+          <t>High Catapult Kick</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>-31</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>-31</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -8160,223 +8120,218 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25_28_30</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>252830</t>
         </is>
       </c>
       <c r="Q88" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>25_28_30</t>
         </is>
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>m</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>m</t>
         </is>
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>d0c56ed6-9bcb-4625-974c-1be79700c41c</t>
+          <t>8e5621a5-277d-4d92-91cc-605997169c4a</t>
         </is>
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>1b19c59d-7afd-4534-a220-93abff3173f8</t>
+          <t>d51c082a-af11-40a0-a5eb-cc54a6413356</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>FC+ub</t>
+          <t>FC+UB+3+4</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>FC+ub</t>
+          <t>FC+UB+3+4</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>FC+u; FC+uf</t>
+          <t>FC+U+3+4; FC+UF+3+4</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Fake Somersault</t>
+          <t>Rainbow Kick</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Fake Somersault</t>
+          <t>Rainbow Kick</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>KD</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="Q89" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>M</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>M</t>
         </is>
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>0d3f2288-0f35-4bef-9004-9a27d304d02d</t>
+          <t>d0c56ed6-9bcb-4625-974c-1be79700c41c</t>
         </is>
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>60a8b811-d5d8-4c28-8646-ada1640d9d1a</t>
+          <t>1b19c59d-7afd-4534-a220-93abff3173f8</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>d,df+4</t>
+          <t>FC+ub</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>d,df+4</t>
+          <t>FC+ub</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>FC+u; FC+uf</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Silver Tail</t>
+          <t>Fake Somersault</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Silver Tail</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>-18</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>-18</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>-7</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>-7</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>+9</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>+9</t>
+          <t>Fake Somersault</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>-</t>
         </is>
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>-</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>OSc RC</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>685285f4-2789-4778-baa6-1d2353b37099</t>
+          <t>0d3f2288-0f35-4bef-9004-9a27d304d02d</t>
         </is>
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>bb762362-40a1-485d-8582-d77d50cd41be</t>
+          <t>60a8b811-d5d8-4c28-8646-ada1640d9d1a</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>– 2,2,1</t>
+          <t>d,df+4</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>d,df+4,2,2,1</t>
+          <t>d,df+4</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>– Silver Demon Fist</t>
+          <t>Silver Tail</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Silver Tail – Silver Demon Fist</t>
+          <t>Silver Tail</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -8384,6 +8339,11 @@
           <t>17</t>
         </is>
       </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>-18</t>
+        </is>
+      </c>
       <c r="J91" t="inlineStr">
         <is>
           <t>-18</t>
@@ -8391,415 +8351,420 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>-7 KD</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>+9 KD</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>18</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>18</t>
         </is>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
-          <t>18,27</t>
+          <t>18</t>
         </is>
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>!</t>
+          <t>L</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>L!</t>
-        </is>
-      </c>
-      <c r="W91" t="inlineStr">
-        <is>
-          <t>This move only works with Kazuya Mishima on your team.</t>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>OSc RC</t>
         </is>
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>b0ccab54-a17c-4b7e-b182-f456aefd98fe</t>
+          <t>685285f4-2789-4778-baa6-1d2353b37099</t>
         </is>
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>8f2b6e2e-2d35-4ad0-a160-7fc8fd9f90b0</t>
-        </is>
-      </c>
-      <c r="AA91" t="inlineStr">
-        <is>
-          <t>685285f4-2789-4778-baa6-1d2353b37099</t>
+          <t>bb762362-40a1-485d-8582-d77d50cd41be</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>f+4</t>
+          <t>– 2,2,1</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>f+4</t>
+          <t>d,df+4,2,2,1</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Silver Knee</t>
+          <t>– Silver Demon Fist</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Silver Knee</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>Silver Tail – Silver Demon Fist</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>-7</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>-7</t>
+          <t>-18</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>-7 KD</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>+9 KD</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>27</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>27</t>
         </is>
       </c>
       <c r="Q92" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>18,27</t>
         </is>
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>!</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>L!</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>This move only works with Kazuya Mishima on your team.</t>
         </is>
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>3d3a292a-f959-4e68-b3f0-0e4b218600e3</t>
+          <t>b0ccab54-a17c-4b7e-b182-f456aefd98fe</t>
         </is>
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>f7638940-dd71-458d-b4e9-6f0020c3abd3</t>
+          <t>8f2b6e2e-2d35-4ad0-a160-7fc8fd9f90b0</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>685285f4-2789-4778-baa6-1d2353b37099</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>b+4 [~3]</t>
+          <t>f+4</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>b+4 [~3]</t>
+          <t>f+4</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Silver Heel [Hit Man Stance]</t>
+          <t>Silver Knee</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Silver Heel [Hit Man Stance]</t>
+          <t>Silver Knee</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-7</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>+8</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>+8</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+4</t>
         </is>
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>h</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="V93" t="inlineStr">
-        <is>
-          <t>BNc</t>
-        </is>
-      </c>
-      <c r="W93" t="inlineStr">
-        <is>
-          <t>No hit is required to buffer a tag after this move.</t>
-        </is>
-      </c>
-      <c r="X93" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+          <t>h</t>
         </is>
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>96cf7074-dd8c-4b40-a94e-b20afb923e00</t>
+          <t>3d3a292a-f959-4e68-b3f0-0e4b218600e3</t>
         </is>
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>05e11dcc-3b52-47d7-ba2a-6bf6c0cb6656</t>
+          <t>f7638940-dd71-458d-b4e9-6f0020c3abd3</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>b,b+4 [~3]</t>
+          <t>b+4</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>b,b+4 [~3]</t>
+          <t>b+4</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Cutter [Hit Man Stance]</t>
+          <t>Silver Heel</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Cutter [Hit Man Stance]</t>
+          <t>Silver Heel</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>(~3)HMS</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>-9</t>
+          <t>-3</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
+          <t>+8</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>+8</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="L94" t="inlineStr">
+      <c r="N94" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
       <c r="O94" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>m</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>BNc</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>No hit is required to buffer a tag after this move.</t>
+        </is>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>5b2fca48-dee4-430a-9737-31438e2ffb94</t>
+          <t>96cf7074-dd8c-4b40-a94e-b20afb923e00</t>
         </is>
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>98a5860f-e778-4085-9eef-fa226502faef</t>
+          <t>05e11dcc-3b52-47d7-ba2a-6bf6c0cb6656</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>d,db+4</t>
+          <t>b,b+4</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>d,db+4</t>
+          <t>b,b+4</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Blazing Kick</t>
+          <t>Cutter</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Blazing Kick</t>
+          <t>Cutter</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>(~3)HMS</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>-19</t>
+          <t>-9</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -8824,166 +8789,166 @@
       </c>
       <c r="O95" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="Q95" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>h</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>JG</t>
-        </is>
-      </c>
-      <c r="X95" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+          <t>h</t>
         </is>
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>e528446b-9678-488e-92c6-c07e210f9929</t>
+          <t>5b2fca48-dee4-430a-9737-31438e2ffb94</t>
         </is>
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10c1f86d-2a18-47b0-80af-82a1175bf046</t>
+          <t>98a5860f-e778-4085-9eef-fa226502faef</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>4,u+3</t>
+          <t>d,db+4</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>4,u+3</t>
+          <t>d,db+4</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Roundhouse - Somersault</t>
+          <t>Blazing Kick</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Roundhouse - Somersault</t>
+          <t>Blazing Kick</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>22</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>-4 -1</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>-4 -1</t>
+          <t>-19</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>+5 KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>+5 KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>KD KD</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>16,30</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>16,30</t>
+          <t>22</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>hm</t>
+          <t>m</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>hm</t>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>506297ed-b796-4ef9-b110-0489d1b46005</t>
+          <t>e528446b-9678-488e-92c6-c07e210f9929</t>
         </is>
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>eeeb82d0-0b32-4cea-9c46-ed7a4c81be38</t>
+          <t>10c1f86d-2a18-47b0-80af-82a1175bf046</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>4,4,4</t>
+          <t>4,u+3</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>4,4,4</t>
+          <t>4,u+3</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Machine Gun Kicks</t>
+          <t>Roundhouse - Somersault</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Machine Gun Kicks</t>
+          <t>Roundhouse - Somersault</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -8998,186 +8963,191 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>-4 -5 -5</t>
+          <t>-4 -1</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>-4 -5 -5</t>
+          <t>-4 -1</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>+5 +4 -5</t>
+          <t>+5 KD</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>+5 +4 -5</t>
+          <t>+5 KD</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>KD KD KD</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>KD KD KD</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>16,8,10</t>
+          <t>16,30</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>46</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>16,8,10</t>
+          <t>16,30</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>hhh</t>
+          <t>hm</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>hhh</t>
+          <t>hm</t>
         </is>
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>83bb6bcf-d942-4843-ba0c-a6841df9d34f</t>
+          <t>506297ed-b796-4ef9-b110-0489d1b46005</t>
         </is>
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>4eccf373-f965-424c-bc9c-414229067f96</t>
+          <t>eeeb82d0-0b32-4cea-9c46-ed7a4c81be38</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>d+4</t>
+          <t>4,4,4</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>d+4</t>
+          <t>4,4,4</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Laser Edge</t>
+          <t>Machine Gun Kicks</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Laser Edge</t>
+          <t>Machine Gun Kicks</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-4 -5 -5</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-4 -5 -5</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>+5 +4 -5</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>+5 +4 -5</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>KD KD KD</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>KD KD KD</t>
         </is>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>16,8,10</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>34</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>16,8,10</t>
         </is>
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>hhh</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>hhh</t>
         </is>
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>c741ed3b-3814-40a0-b687-ae38e16affba</t>
+          <t>83bb6bcf-d942-4843-ba0c-a6841df9d34f</t>
         </is>
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>32a11660-8e58-49db-8740-d4563c8882a5</t>
+          <t>4eccf373-f965-424c-bc9c-414229067f96</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>– &lt;N+4,4,4</t>
+          <t>d+4</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>d+4&lt;N+4,4,4</t>
+          <t>d+4</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>– Machine Gun Kicks</t>
+          <t>Laser Edge</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Laser Edge – Machine Gun Kicks</t>
+          <t>Laser Edge</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>12</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -9187,94 +9157,89 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>-9 -5 -5</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>-11 -9 -5 -5</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>0 +4 +4</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>-12 0 +4 +4</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>KD KD KD</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>-12 KD KD KD</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="O99" t="inlineStr">
         <is>
-          <t>20,8,10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Q99" t="inlineStr">
         <is>
-          <t>7,20,8,10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>hhh</t>
+          <t>l</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>lhhh</t>
+          <t>l</t>
         </is>
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>31d00669-84fb-4412-b68a-6c111dbe11e3</t>
+          <t>c741ed3b-3814-40a0-b687-ae38e16affba</t>
         </is>
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>d2888831-42f0-4632-8896-df78cc983ee0</t>
-        </is>
-      </c>
-      <c r="AA99" t="inlineStr">
-        <is>
-          <t>c741ed3b-3814-40a0-b687-ae38e16affba</t>
+          <t>32a11660-8e58-49db-8740-d4563c8882a5</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>– ~N+4~3</t>
+          <t>– &lt;N+4,4,4</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>d+4~N+4~3</t>
+          <t>d+4&lt;N+4,4,4</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>– Silver Cyclone</t>
+          <t>– Machine Gun Kicks</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Laser Edge – Silver Cyclone</t>
+          <t>Laser Edge – Machine Gun Kicks</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -9282,49 +9247,69 @@
           <t>12</t>
         </is>
       </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>-9 -5 -5</t>
+        </is>
+      </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-11 -9 -5 -5</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>0 +4 +4</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-12 0 +4 +4</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>KD KD KD</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-12 KD KD KD</t>
         </is>
       </c>
       <c r="O100" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>20,8,10</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>38</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t>7,80</t>
+          <t>7,20,8,10</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>hhh</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>l</t>
+          <t>lhhh</t>
         </is>
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>f4257d79-9450-49cb-b78e-7f47f07f1f9f</t>
+          <t>31d00669-84fb-4412-b68a-6c111dbe11e3</t>
         </is>
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>732b8adf-d76c-4d2b-9087-4b978acbc071</t>
+          <t>d2888831-42f0-4632-8896-df78cc983ee0</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -9336,22 +9321,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>– &lt;N+4,3,4</t>
+          <t>– ~N+4~3</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>d+4&lt;N+4,3,4</t>
+          <t>d+4~N+4~3</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>– Shoalin Spin Kicks</t>
+          <t>– Silver Cyclone</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Laser Edge – Shoalin Spin Kicks</t>
+          <t>Laser Edge – Silver Cyclone</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -9359,69 +9344,49 @@
           <t>12</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>-9 -14 -6</t>
-        </is>
-      </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>-11 -9 -14 -6</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>0 -17 -1</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>-12 0 -17 -1</t>
-        </is>
-      </c>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>0 -17 KD</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>-12 0 -17 KD</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
         <is>
-          <t>20,12,12</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>80</t>
         </is>
       </c>
       <c r="Q101" t="inlineStr">
         <is>
-          <t>7,20,12,12</t>
-        </is>
-      </c>
-      <c r="R101" t="inlineStr">
-        <is>
-          <t>hhh</t>
+          <t>7,80</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>lhhh</t>
+          <t>l</t>
         </is>
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>798de36b-3da2-486e-937c-ac9ce407c6ad</t>
+          <t>f4257d79-9450-49cb-b78e-7f47f07f1f9f</t>
         </is>
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>7b81cccd-a64e-457e-853d-c3697becb8e0</t>
+          <t>732b8adf-d76c-4d2b-9087-4b978acbc071</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -9433,22 +9398,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>– &lt;N+4,u+3</t>
+          <t>– &lt;N+4,3,4</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>d+4&lt;N+4,u+3</t>
+          <t>d+4&lt;N+4,3,4</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>– Roundhouse - Somersault</t>
+          <t>– Shoalin Spin Kicks</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Laser Edge – Roundhouse - Somersault</t>
+          <t>Laser Edge – Shoalin Spin Kicks</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -9458,72 +9423,67 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>-9 -1</t>
+          <t>-9 -14 -6</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>-11 -9 -1</t>
+          <t>-11 -9 -14 -6</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>0 KD</t>
+          <t>0 -17 -1</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>-12 0 KD</t>
+          <t>-12 0 -17 -1</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>0 KD</t>
+          <t>0 -17 KD</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>-12 0 KD</t>
+          <t>-12 0 -17 KD</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
         <is>
-          <t>20,30</t>
+          <t>20,12,12</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>44</t>
         </is>
       </c>
       <c r="Q102" t="inlineStr">
         <is>
-          <t>7,20,30</t>
+          <t>7,20,12,12</t>
         </is>
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>hm</t>
+          <t>hhh</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>lhm</t>
-        </is>
-      </c>
-      <c r="X102" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+          <t>lhhh</t>
         </is>
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>691d70f5-4574-4ae3-b82d-87a60db93828</t>
+          <t>798de36b-3da2-486e-937c-ac9ce407c6ad</t>
         </is>
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>cfeb519a-0dec-46ee-babc-694f1ee60a45</t>
+          <t>7b81cccd-a64e-457e-853d-c3697becb8e0</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -9535,532 +9495,582 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>D+4&lt;4&lt;4&lt;4 [~3]</t>
+          <t>– &lt;N+4,u+3</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>D+4&lt;4&lt;4&lt;4 [~3]</t>
+          <t>d+4&lt;N+4,u+3</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Laser Edge Rush [Hit Man Stance]</t>
+          <t>– Roundhouse - Somersault</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Laser Edge Rush [Hit Man Stance]</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
+          <t>Laser Edge – Roundhouse - Somersault</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>-11 -20 -25 -20</t>
+          <t>-9 -1</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>-11 -20 -25 -20</t>
+          <t>-11 -9 -1</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>-12 -21 -14 KD</t>
+          <t>0 KD</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>-12 -21 -14 KD</t>
+          <t>-12 0 KD</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>-12 -21 -14 KD</t>
+          <t>0 KD</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>-12 -21 -14 KD</t>
+          <t>-12 0 KD</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>7,5,5,21</t>
+          <t>20,30</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>50</t>
         </is>
       </c>
       <c r="Q103" t="inlineStr">
         <is>
-          <t>7,5,5,21</t>
+          <t>7,20,30</t>
         </is>
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>lllm</t>
+          <t>hm</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>lllm</t>
+          <t>lhm</t>
+        </is>
+      </c>
+      <c r="X103" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>80993965-6214-47a8-a5aa-f15fddcf516d</t>
+          <t>691d70f5-4574-4ae3-b82d-87a60db93828</t>
         </is>
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>335cf006-8326-46e2-a623-ee50ce398492</t>
+          <t>cfeb519a-0dec-46ee-babc-694f1ee60a45</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>c741ed3b-3814-40a0-b687-ae38e16affba</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>3+4</t>
+          <t>D+4&lt;4&lt;4&lt;4</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>3+4</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>3~4</t>
+          <t>D+4&lt;4&lt;4&lt;4</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Hit Man Stance</t>
+          <t>Laser Edge Rush</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Hit Man Stance</t>
+          <t>Laser Edge Rush</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>HMS</t>
+          <t>(~3)HMS</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>-11 -20 -25 -20</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>-11 -20 -25 -20</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>-12 -21 -14 KD</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>-12 -21 -14 KD</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>-12 -21 -14 KD</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>-12 -21 -14 KD</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7,5,5,21</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7,5,5,21</t>
         </is>
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>lllm</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>lllm</t>
         </is>
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>3723aec3-67d3-4812-b814-d46090c8ef43</t>
+          <t>80993965-6214-47a8-a5aa-f15fddcf516d</t>
         </is>
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>52118ae8-1c85-4f79-bace-87287a3db69a</t>
+          <t>335cf006-8326-46e2-a623-ee50ce398492</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
+          <t>3+4</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>3+4</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>3~4</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Hit Man Stance</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Hit Man Stance</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>HMS</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>3723aec3-67d3-4812-b814-d46090c8ef43</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>52118ae8-1c85-4f79-bace-87287a3db69a</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
           <t>f,N</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B106" t="inlineStr">
         <is>
           <t>f,N</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
+      <c r="D106" t="inlineStr">
         <is>
           <t>Mist Step</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
+      <c r="E106" t="inlineStr">
         <is>
           <t>Mist Step</t>
         </is>
       </c>
-      <c r="O105" t="inlineStr">
+      <c r="O106" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P105" t="inlineStr">
+      <c r="P106" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q105" t="inlineStr">
+      <c r="Q106" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R105" t="inlineStr">
+      <c r="R106" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S105" t="inlineStr">
+      <c r="S106" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y105" t="inlineStr">
+      <c r="Y106" t="inlineStr">
         <is>
           <t>dc2aaa39-a764-4001-bbeb-f5d35135a4cb</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr">
+      <c r="Z106" t="inlineStr">
         <is>
           <t>d96c06e7-716e-485d-8781-dab6f2506107</t>
         </is>
       </c>
     </row>
-    <row r="106"/>
-    <row r="107">
-      <c r="A107" s="1" t="inlineStr">
-        <is>
-          <t>Hit Man Arts</t>
-        </is>
-      </c>
-    </row>
+    <row r="107"/>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
+          <t>Hit Man Arts</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="inlineStr">
+        <is>
           <t>Command</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
+      <c r="B109" s="1" t="inlineStr">
         <is>
           <t>Command Full</t>
         </is>
       </c>
-      <c r="C108" s="1" t="inlineStr">
+      <c r="C109" s="1" t="inlineStr">
         <is>
           <t>Alt Commands</t>
         </is>
       </c>
-      <c r="D108" s="1" t="inlineStr">
+      <c r="D109" s="1" t="inlineStr">
         <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="E108" s="1" t="inlineStr">
+      <c r="E109" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="F108" s="1" t="inlineStr">
+      <c r="F109" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="G108" s="1" t="inlineStr">
+      <c r="G109" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="H108" s="1" t="inlineStr">
+      <c r="H109" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="I108" s="1" t="inlineStr">
+      <c r="I109" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="J108" s="1" t="inlineStr">
+      <c r="J109" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="K108" s="1" t="inlineStr">
+      <c r="K109" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="L108" s="1" t="inlineStr">
+      <c r="L109" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="M108" s="1" t="inlineStr">
+      <c r="M109" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="N108" s="1" t="inlineStr">
+      <c r="N109" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="O108" s="1" t="inlineStr">
+      <c r="O109" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="P108" s="1" t="inlineStr">
+      <c r="P109" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="Q108" s="1" t="inlineStr">
+      <c r="Q109" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="R108" s="1" t="inlineStr">
+      <c r="R109" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="S108" s="1" t="inlineStr">
+      <c r="S109" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="T108" s="1" t="inlineStr">
+      <c r="T109" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="U108" s="1" t="inlineStr">
+      <c r="U109" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="V108" s="1" t="inlineStr">
+      <c r="V109" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="W108" s="1" t="inlineStr">
+      <c r="W109" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="X108" s="1" t="inlineStr">
+      <c r="X109" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Y108" s="1" t="inlineStr">
+      <c r="Y109" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Z108" s="1" t="inlineStr">
+      <c r="Z109" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AA108" s="1" t="inlineStr">
+      <c r="AA109" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AB108" s="1" t="inlineStr">
+      <c r="AB109" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Moves from HMS only</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Moves from HMS only</t>
-        </is>
-      </c>
-      <c r="Y109" t="inlineStr">
-        <is>
-          <t>cf57b3dd-1af7-4c8d-bb66-57da517ace91</t>
-        </is>
-      </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>423595c7-5b74-4eb1-ae7d-ed0ff3ab58f3</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1,1...</t>
+          <t>Moves from HMS only</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>1,1...</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>Freaker Jabs</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>Freaker Jabs</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>HMS</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>0 0</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>0 0</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>+9 +9</t>
-        </is>
-      </c>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>+9 +9</t>
-        </is>
-      </c>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>+9 +9</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr">
-        <is>
-          <t>+9 +9</t>
-        </is>
-      </c>
-      <c r="O110" t="inlineStr">
-        <is>
-          <t>15,12...</t>
-        </is>
-      </c>
-      <c r="P110" t="inlineStr">
-        <is>
-          <t>15,12...</t>
-        </is>
-      </c>
-      <c r="Q110" t="inlineStr">
-        <is>
-          <t>15,12...</t>
-        </is>
-      </c>
-      <c r="R110" t="inlineStr">
-        <is>
-          <t>h</t>
-        </is>
-      </c>
-      <c r="S110" t="inlineStr">
-        <is>
-          <t>h</t>
+          <t>Moves from HMS only</t>
         </is>
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>6646a0dc-4159-4937-b505-272f9a063e54</t>
+          <t>cf57b3dd-1af7-4c8d-bb66-57da517ace91</t>
         </is>
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>30ed043e-2bbc-4228-b286-7adffd47ce93</t>
+          <t>423595c7-5b74-4eb1-ae7d-ed0ff3ab58f3</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1,3</t>
+          <t>1,1...</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>1,3</t>
+          <t>1,1...</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Fake Freaker Scatter Kick</t>
+          <t>Freaker Jabs</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Fake Freaker Scatter Kick</t>
+          <t>Freaker Jabs</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>HMS</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>0 0</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>0 0</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>+9 +9</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>+9 +9</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>+9 +9</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>+9 +9</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>21,13</t>
+          <t>15,12...</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>15,12...</t>
         </is>
       </c>
       <c r="Q111" t="inlineStr">
         <is>
-          <t>21,13</t>
+          <t>15,12...</t>
         </is>
       </c>
       <c r="R111" t="inlineStr">
@@ -10075,161 +10085,111 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>d3fe3cb9-0406-4b77-b524-f8460a5b4920</t>
+          <t>6646a0dc-4159-4937-b505-272f9a063e54</t>
         </is>
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>28c75535-deed-4cd1-ac6a-50ece377b500</t>
+          <t>30ed043e-2bbc-4228-b286-7adffd47ce93</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1,3</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1,3</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Scatter Blow</t>
+          <t>Fake Freaker Scatter Kick</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Scatter Blow</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>-6</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>-6</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr">
-        <is>
-          <t>KD</t>
+          <t>Fake Freaker Scatter Kick</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21,13</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>34</t>
         </is>
       </c>
       <c r="Q112" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21,13</t>
         </is>
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>h</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="V112" t="inlineStr">
-        <is>
-          <t>JG GB</t>
-        </is>
-      </c>
-      <c r="X112" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+          <t>h</t>
         </is>
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>c656c60e-b30b-4cf9-8510-2f483899d74f</t>
+          <t>d3fe3cb9-0406-4b77-b524-f8460a5b4920</t>
         </is>
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>c8dbf919-d096-4ab7-9ee3-ef6721364316</t>
+          <t>28c75535-deed-4cd1-ac6a-50ece377b500</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Scatter Kick</t>
+          <t>Scatter Blow</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Scatter Kick</t>
+          <t>Scatter Blow</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -10254,79 +10214,89 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>21,13</t>
+          <t>23</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
-          <t>21,13</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>m</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>JG GB</t>
+        </is>
+      </c>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>a90fbdce-f88d-4ca7-ba70-2e9575ff0f88</t>
+          <t>c656c60e-b30b-4cf9-8510-2f483899d74f</t>
         </is>
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>a44b9614-84bb-42b3-8db2-76ecc6fd1bb1</t>
+          <t>c8dbf919-d096-4ab7-9ee3-ef6721364316</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Ship Slicer</t>
+          <t>Scatter Kick</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Ship Slicer</t>
+          <t>Scatter Kick</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>17</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>-22</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>-22</t>
+          <t>-10</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -10351,126 +10321,156 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21,13</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>34</t>
         </is>
       </c>
       <c r="Q114" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21,13</t>
         </is>
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>h</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>L</t>
-        </is>
-      </c>
-      <c r="V114" t="inlineStr">
-        <is>
-          <t>JG GB RC</t>
+          <t>h</t>
         </is>
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>40d410c0-9905-4c23-aa63-3ab9eee3bcc6</t>
+          <t>a90fbdce-f88d-4ca7-ba70-2e9575ff0f88</t>
         </is>
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>67dce5e4-a024-4cd9-9bd8-90b796b08756</t>
+          <t>a44b9614-84bb-42b3-8db2-76ecc6fd1bb1</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>f</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>b</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Hit Man Cancel</t>
+          <t>Ship Slicer</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Hit Man Cancel</t>
+          <t>Ship Slicer</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>-22</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>-22</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>KD</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q115" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>L</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="W115" t="inlineStr">
-        <is>
-          <t>During the cancel animation from Hit Man to regular stance you can still execute Hit Man kick attacks.</t>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>JG GB RC</t>
         </is>
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>013588b5-0299-4731-969e-d97a8d4599f7</t>
+          <t>40d410c0-9905-4c23-aa63-3ab9eee3bcc6</t>
         </is>
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>e1762469-ce15-40b2-820d-f76ee6c6c1c3</t>
+          <t>67dce5e4-a024-4cd9-9bd8-90b796b08756</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>f</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>f</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>b</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -10510,722 +10510,789 @@
       </c>
       <c r="W116" t="inlineStr">
         <is>
-          <t>During the cancel animation from Hit Man to regular stance you can still execute all Hit Man attacks.</t>
+          <t>During the cancel animation from Hit Man to regular stance you can still execute Hit Man kick attacks.</t>
         </is>
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>99415844-7ae1-4140-84a8-901dcecfe4dc</t>
+          <t>013588b5-0299-4731-969e-d97a8d4599f7</t>
         </is>
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>1564bc75-570c-417d-8e40-fb89963d5655</t>
+          <t>e1762469-ce15-40b2-820d-f76ee6c6c1c3</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Hit Man Cancel</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Hit Man Cancel</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>During the cancel animation from Hit Man to regular stance you can still execute all Hit Man attacks.</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>99415844-7ae1-4140-84a8-901dcecfe4dc</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>1564bc75-570c-417d-8e40-fb89963d5655</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
           <t>u</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
+      <c r="B118" t="inlineStr">
         <is>
           <t>u</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
+      <c r="C118" t="inlineStr">
         <is>
           <t>d</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
+      <c r="D118" t="inlineStr">
         <is>
           <t>Predator Step</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
+      <c r="E118" t="inlineStr">
         <is>
           <t>Predator Step</t>
         </is>
       </c>
-      <c r="O117" t="inlineStr">
+      <c r="O118" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P117" t="inlineStr">
+      <c r="P118" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q117" t="inlineStr">
+      <c r="Q118" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R117" t="inlineStr">
+      <c r="R118" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S117" t="inlineStr">
+      <c r="S118" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Y117" t="inlineStr">
+      <c r="Y118" t="inlineStr">
         <is>
           <t>bcb9cd71-aca0-4947-865b-56c5bb8a947a</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
+      <c r="Z118" t="inlineStr">
         <is>
           <t>00a021af-262e-4398-a5ee-8deccead2dde</t>
         </is>
       </c>
     </row>
-    <row r="118"/>
-    <row r="119">
-      <c r="A119" s="1" t="inlineStr">
-        <is>
-          <t>Unblockable Arts</t>
-        </is>
-      </c>
-    </row>
+    <row r="119"/>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
+          <t>Unblockable Arts</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="inlineStr">
+        <is>
           <t>Command</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
+      <c r="B121" s="1" t="inlineStr">
         <is>
           <t>Command Full</t>
         </is>
       </c>
-      <c r="C120" s="1" t="inlineStr">
+      <c r="C121" s="1" t="inlineStr">
         <is>
           <t>Alt Commands</t>
         </is>
       </c>
-      <c r="D120" s="1" t="inlineStr">
+      <c r="D121" s="1" t="inlineStr">
         <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="E120" s="1" t="inlineStr">
+      <c r="E121" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="F120" s="1" t="inlineStr">
+      <c r="F121" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="G120" s="1" t="inlineStr">
+      <c r="G121" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="H120" s="1" t="inlineStr">
+      <c r="H121" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="I120" s="1" t="inlineStr">
+      <c r="I121" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="J120" s="1" t="inlineStr">
+      <c r="J121" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="K120" s="1" t="inlineStr">
+      <c r="K121" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="L120" s="1" t="inlineStr">
+      <c r="L121" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="M120" s="1" t="inlineStr">
+      <c r="M121" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="N120" s="1" t="inlineStr">
+      <c r="N121" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="O120" s="1" t="inlineStr">
+      <c r="O121" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="P120" s="1" t="inlineStr">
+      <c r="P121" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="Q120" s="1" t="inlineStr">
+      <c r="Q121" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="R120" s="1" t="inlineStr">
+      <c r="R121" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="S120" s="1" t="inlineStr">
+      <c r="S121" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="T120" s="1" t="inlineStr">
+      <c r="T121" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="U120" s="1" t="inlineStr">
+      <c r="U121" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="V120" s="1" t="inlineStr">
+      <c r="V121" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="W120" s="1" t="inlineStr">
+      <c r="W121" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="X120" s="1" t="inlineStr">
+      <c r="X121" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Y120" s="1" t="inlineStr">
+      <c r="Y121" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Z120" s="1" t="inlineStr">
+      <c r="Z121" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AA120" s="1" t="inlineStr">
+      <c r="AA121" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AB120" s="1" t="inlineStr">
+      <c r="AB121" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>d+3+4</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>d+3+4</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>Silver Cyclone</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>Silver Cyclone</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="L121" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="N121" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="O121" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="P121" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="Q121" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="Y121" t="inlineStr">
-        <is>
-          <t>de1359c9-8fd1-4c28-aeb2-1295c434945b</t>
-        </is>
-      </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>a97cf13d-190d-4e1c-964e-5333112147e7</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>d+4,N+4~3</t>
+          <t>d+3+4</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>d+4,N+4~3</t>
+          <t>d+3+4</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Low Cancel Silver Cyclone</t>
+          <t>Silver Cyclone</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Low Cancel Silver Cyclone</t>
+          <t>Silver Cyclone</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>KD</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>7,80</t>
+          <t>80</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>80</t>
         </is>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>7,80</t>
-        </is>
-      </c>
-      <c r="R122" t="inlineStr">
-        <is>
-          <t>l,</t>
-        </is>
-      </c>
-      <c r="S122" t="inlineStr">
-        <is>
-          <t>l,</t>
+          <t>80</t>
         </is>
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>fa09c625-67c8-4250-a487-fd848aa52406</t>
+          <t>de1359c9-8fd1-4c28-aeb2-1295c434945b</t>
         </is>
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>52004fa2-9050-4d75-94cc-45a642c0febd</t>
+          <t>a97cf13d-190d-4e1c-964e-5333112147e7</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>db+1+2</t>
+          <t>d+4,N+4~3</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>db+1+2</t>
+          <t>d+4,N+4~3</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Silver Fang</t>
+          <t>Low Cancel Silver Cyclone</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Silver Fang</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="L123" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="N123" t="inlineStr">
-        <is>
-          <t>KD</t>
+          <t>Low Cancel Silver Cyclone</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>7,80</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>87</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>7,80</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>!</t>
+          <t>l,</t>
         </is>
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>!</t>
+          <t>l,</t>
         </is>
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>ad99b613-27f9-4d35-b5c5-76e65296ba01</t>
+          <t>fa09c625-67c8-4250-a487-fd848aa52406</t>
         </is>
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>5375bf00-d974-4c04-ae55-9b3afa9068e8</t>
+          <t>52004fa2-9050-4d75-94cc-45a642c0febd</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
+          <t>db+1+2</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>db+1+2</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Silver Fang</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Silver Fang</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>!</t>
+        </is>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>!</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>ad99b613-27f9-4d35-b5c5-76e65296ba01</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>5375bf00-d974-4c04-ae55-9b3afa9068e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
           <t>– u,u</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
+      <c r="B125" t="inlineStr">
         <is>
           <t>db+1+2,u,u</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr">
+      <c r="D125" t="inlineStr">
         <is>
           <t>– Cancel</t>
         </is>
       </c>
-      <c r="E124" t="inlineStr">
+      <c r="E125" t="inlineStr">
         <is>
           <t>Silver Fang – Cancel</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
+      <c r="H125" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="L124" t="inlineStr">
+      <c r="L125" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N124" t="inlineStr">
+      <c r="N125" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O124" t="inlineStr">
+      <c r="O125" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P124" t="inlineStr">
+      <c r="P125" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q124" t="inlineStr">
+      <c r="Q125" t="inlineStr">
         <is>
           <t>100,-</t>
         </is>
       </c>
-      <c r="R124" t="inlineStr">
+      <c r="R125" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S124" t="inlineStr">
+      <c r="S125" t="inlineStr">
         <is>
           <t>!-</t>
         </is>
       </c>
-      <c r="Y124" t="inlineStr">
+      <c r="Y125" t="inlineStr">
         <is>
           <t>75ab88a8-f58b-4aec-8231-00ac8e5f2cc2</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr">
+      <c r="Z125" t="inlineStr">
         <is>
           <t>582cdbb3-74de-4a6e-ad91-713bd28117d8</t>
         </is>
       </c>
-      <c r="AA124" t="inlineStr">
+      <c r="AA125" t="inlineStr">
         <is>
           <t>ad99b613-27f9-4d35-b5c5-76e65296ba01</t>
         </is>
       </c>
     </row>
-    <row r="125"/>
-    <row r="126">
-      <c r="A126" s="1" t="inlineStr">
-        <is>
-          <t>String Hit Arts</t>
-        </is>
-      </c>
-    </row>
+    <row r="126"/>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
+          <t>String Hit Arts</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="inlineStr">
+        <is>
           <t>Command</t>
         </is>
       </c>
-      <c r="B127" s="1" t="inlineStr">
+      <c r="B128" s="1" t="inlineStr">
         <is>
           <t>Command Full</t>
         </is>
       </c>
-      <c r="C127" s="1" t="inlineStr">
+      <c r="C128" s="1" t="inlineStr">
         <is>
           <t>Alt Commands</t>
         </is>
       </c>
-      <c r="D127" s="1" t="inlineStr">
+      <c r="D128" s="1" t="inlineStr">
         <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="E127" s="1" t="inlineStr">
+      <c r="E128" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="F127" s="1" t="inlineStr">
+      <c r="F128" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="G127" s="1" t="inlineStr">
+      <c r="G128" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="H127" s="1" t="inlineStr">
+      <c r="H128" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="I127" s="1" t="inlineStr">
+      <c r="I128" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="J127" s="1" t="inlineStr">
+      <c r="J128" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="K127" s="1" t="inlineStr">
+      <c r="K128" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="L127" s="1" t="inlineStr">
+      <c r="L128" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="M127" s="1" t="inlineStr">
+      <c r="M128" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="N127" s="1" t="inlineStr">
+      <c r="N128" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="O127" s="1" t="inlineStr">
+      <c r="O128" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="P127" s="1" t="inlineStr">
+      <c r="P128" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="Q127" s="1" t="inlineStr">
+      <c r="Q128" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="R127" s="1" t="inlineStr">
+      <c r="R128" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="S127" s="1" t="inlineStr">
+      <c r="S128" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="T127" s="1" t="inlineStr">
+      <c r="T128" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="U127" s="1" t="inlineStr">
+      <c r="U128" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="V127" s="1" t="inlineStr">
+      <c r="V128" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="W127" s="1" t="inlineStr">
+      <c r="W128" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="X127" s="1" t="inlineStr">
+      <c r="X128" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Y127" s="1" t="inlineStr">
+      <c r="Y128" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="Z127" s="1" t="inlineStr">
+      <c r="Z128" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AA127" s="1" t="inlineStr">
+      <c r="AA128" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AB127" s="1" t="inlineStr">
+      <c r="AB128" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
+    <row r="129">
+      <c r="A129" t="inlineStr">
         <is>
           <t>df+1,2,2,1,3,3,3,4,3,4</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
+      <c r="B129" t="inlineStr">
         <is>
           <t>df+1,2,2,1,3,3,3,4,3,4</t>
         </is>
       </c>
-      <c r="O128" t="inlineStr">
+      <c r="O129" t="inlineStr">
         <is>
           <t>10,5,6,5,7,6,7,7,10,25</t>
         </is>
       </c>
-      <c r="P128" t="inlineStr">
+      <c r="P129" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="Q128" t="inlineStr">
+      <c r="Q129" t="inlineStr">
         <is>
           <t>10,5,6,5,7,6,7,7,10,25</t>
         </is>
       </c>
-      <c r="R128" t="inlineStr">
+      <c r="R129" t="inlineStr">
         <is>
           <t>mhmhhLhhhm</t>
         </is>
       </c>
-      <c r="S128" t="inlineStr">
+      <c r="S129" t="inlineStr">
         <is>
           <t>mhmhhLhhhm</t>
         </is>
       </c>
-      <c r="Z128" t="inlineStr">
+      <c r="Z129" t="inlineStr">
         <is>
           <t>5508724d-2532-494e-91ba-e198355b8ea4</t>
         </is>
       </c>
-      <c r="AB128" t="inlineStr">
+      <c r="AB129" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>

--- a/sources/lee_step8.xlsx
+++ b/sources/lee_step8.xlsx
@@ -861,6 +861,11 @@
           <t>When done with 2+4 against Bryan, he will laugh back at Lee and sometimes gain a little energy back.</t>
         </is>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>b066f77f-2cf9-45e9-ae19-41234876127b</t>
+        </is>
+      </c>
       <c r="Z6" t="inlineStr">
         <is>
           <t>b066f77f-2cf9-45e9-ae19-41234876127b</t>
@@ -923,6 +928,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>b186cd07-1f81-4494-bf28-78196461652c</t>
+        </is>
+      </c>
       <c r="Z7" t="inlineStr">
         <is>
           <t>b186cd07-1f81-4494-bf28-78196461652c</t>
@@ -983,6 +993,11 @@
       <c r="U8" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>9736f543-5f0b-4d41-9d88-4dba289c8e13</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -11285,6 +11300,11 @@
       <c r="S129" t="inlineStr">
         <is>
           <t>mhmhhLhhhm</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>5508724d-2532-494e-91ba-e198355b8ea4</t>
         </is>
       </c>
       <c r="Z129" t="inlineStr">
